--- a/reports/raw-views/assets/tables/micro_semantic_richness_agents.xlsx
+++ b/reports/raw-views/assets/tables/micro_semantic_richness_agents.xlsx
@@ -436,42 +436,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Autores score 1</t>
+          <t>Authors score 1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Autores score 3</t>
+          <t>Authors score 3</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Autores score 5</t>
+          <t>Authors score 5</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Pares</t>
+          <t>Peers</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Analistas SV</t>
+          <t>Analysts SV</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Analistas VS</t>
+          <t>Analysts VS</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>IA ChatGPT</t>
+          <t>AI ChatGPT</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>IA Gemini</t>
+          <t>AI Gemini</t>
         </is>
       </c>
     </row>
